--- a/data/memories/memory_01/locales/es/documents/reception/Meeting_Room_Bookings.xlsx
+++ b/data/memories/memory_01/locales/es/documents/reception/Meeting_Room_Bookings.xlsx
@@ -433,7 +433,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Meeting Room Bookings</t>
+          <t>Reservas de salas de reuniones</t>
         </is>
       </c>
     </row>
@@ -445,7 +445,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Interno</t>
         </is>
       </c>
     </row>
@@ -469,36 +469,36 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Reception</t>
+          <t>Recepción</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Bookings</t>
+          <t>Reservas</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Tiempo</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Room</t>
+          <t>Habitación</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Purpose</t>
+          <t>Objetivo</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Host</t>
+          <t>Anfitrión</t>
         </is>
       </c>
     </row>
@@ -510,12 +510,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Meeting Room A</t>
+          <t>Sala de reuniones A</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>Preparación</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -532,12 +532,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Meeting Room A</t>
+          <t>Sala de reuniones A</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Weekly Management Meeting</t>
+          <t>Reunión Gerencial Semanal</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Meeting Room A</t>
+          <t>Sala de reuniones A</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Internal Meeting</t>
+          <t>Reunión Interna</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
